--- a/ExcelToTemplate/Source.xlsx
+++ b/ExcelToTemplate/Source.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cnavera\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cf76eb68cee54fc3/Documents/GitHub/python-training/ExcelToTemplate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB94D184-D953-40F7-8488-7B4163CAA677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{AB94D184-D953-40F7-8488-7B4163CAA677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F4DCA1F-07AA-4546-8AE7-D9CE417002C8}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="624" xr2:uid="{051F5F2F-B49F-4F58-BE02-03C05ADD24A6}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="624" xr2:uid="{051F5F2F-B49F-4F58-BE02-03C05ADD24A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Rig Information" sheetId="1" r:id="rId1"/>
@@ -2172,7 +2172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2314,49 +2314,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -3476,7 +3438,7 @@
         <v>199</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J2" s="26" t="s">
         <v>70</v>
@@ -8067,156 +8029,141 @@
       <c r="DM19" s="34"/>
       <c r="DN19" s="34"/>
     </row>
-    <row r="20" spans="1:118" s="55" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:118" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="44" t="s">
         <v>225</v>
       </c>
       <c r="B20" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="46">
+      <c r="C20" s="25">
         <v>9624158</v>
       </c>
-      <c r="D20" s="47">
+      <c r="D20" s="26">
         <v>10623</v>
       </c>
-      <c r="E20" s="47" t="s">
+      <c r="E20" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="F20" s="48" t="s">
+      <c r="F20" s="27" t="s">
         <v>201</v>
       </c>
-      <c r="G20" s="47" t="s">
+      <c r="G20" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="H20" s="47" t="s">
+      <c r="H20" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="I20" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="J20" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="K20" s="49"/>
-      <c r="L20" s="49"/>
-      <c r="M20" s="47" t="s">
+      <c r="I20" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="J20" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="M20" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="N20" s="47" t="s">
+      <c r="N20" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="O20" s="50" t="s">
+      <c r="O20" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="P20" s="50" t="s">
+      <c r="P20" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="Q20" s="50" t="s">
+      <c r="Q20" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="R20" s="50" t="s">
+      <c r="R20" s="28" t="s">
         <v>301</v>
       </c>
-      <c r="S20" s="47" t="s">
+      <c r="S20" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="T20" s="47" t="s">
+      <c r="T20" s="26" t="s">
         <v>299</v>
       </c>
-      <c r="U20" s="50" t="s">
+      <c r="U20" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="V20" s="50" t="s">
+      <c r="V20" s="28" t="s">
         <v>300</v>
       </c>
-      <c r="W20" s="47" t="s">
+      <c r="W20" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="X20" s="47" t="s">
+      <c r="X20" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="Y20" s="47" t="s">
+      <c r="Y20" s="26" t="s">
         <v>293</v>
       </c>
-      <c r="Z20" s="51" t="s">
+      <c r="Z20" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="AA20" s="48" t="s">
+      <c r="AA20" s="27" t="s">
         <v>286</v>
       </c>
-      <c r="AB20" s="48" t="s">
+      <c r="AB20" s="27" t="s">
         <v>286</v>
       </c>
       <c r="AC20" s="28" t="s">
         <v>295</v>
       </c>
       <c r="AD20" s="26"/>
-      <c r="AE20" s="50" t="s">
+      <c r="AE20" s="28" t="s">
         <v>230</v>
       </c>
-      <c r="AF20" s="50" t="s">
+      <c r="AF20" s="28" t="s">
         <v>296</v>
       </c>
-      <c r="AG20" s="47" t="s">
+      <c r="AG20" s="26" t="s">
         <v>297</v>
       </c>
-      <c r="AH20" s="47" t="s">
+      <c r="AH20" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="AI20" s="49"/>
-      <c r="AJ20" s="49"/>
-      <c r="AK20" s="49"/>
-      <c r="AL20" s="49"/>
-      <c r="AM20" s="49"/>
-      <c r="AN20" s="49"/>
-      <c r="AO20" s="49"/>
-      <c r="AP20" s="49"/>
-      <c r="AQ20" s="49"/>
-      <c r="AR20" s="49"/>
-      <c r="AS20" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="AT20" s="52" t="s">
-        <v>85</v>
-      </c>
-      <c r="AU20" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="AV20" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="AW20" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="AX20" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY20" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="AZ20" s="53" t="s">
-        <v>86</v>
-      </c>
-      <c r="BA20" s="53" t="s">
-        <v>86</v>
-      </c>
-      <c r="BB20" s="49"/>
-      <c r="BC20" s="49"/>
-      <c r="BD20" s="49"/>
-      <c r="BE20" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="BF20" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="BG20" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="BH20" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="BI20" s="53" t="s">
+      <c r="AS20" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT20" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="AU20" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV20" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW20" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="AX20" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="AY20" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="AZ20" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="BA20" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="BE20" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="BF20" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="BG20" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="BH20" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="BI20" s="31" t="s">
         <v>86</v>
       </c>
       <c r="BJ20" s="26" t="s">
@@ -8225,83 +8172,39 @@
       <c r="BK20" s="26" t="s">
         <v>305</v>
       </c>
-      <c r="BL20" s="47" t="s">
+      <c r="BL20" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="BM20" s="47"/>
-      <c r="BN20" s="47" t="s">
+      <c r="BN20" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="BO20" s="47" t="s">
+      <c r="BO20" s="26" t="s">
         <v>273</v>
       </c>
-      <c r="BP20" s="47" t="s">
+      <c r="BP20" s="26" t="s">
         <v>274</v>
       </c>
-      <c r="BQ20" s="47">
+      <c r="BQ20" s="26">
         <v>77042</v>
       </c>
-      <c r="BR20" s="47"/>
       <c r="BS20" s="35" t="s">
         <v>303</v>
       </c>
-      <c r="BT20" s="47"/>
-      <c r="BU20" s="47" t="s">
+      <c r="BU20" s="26" t="s">
         <v>257</v>
       </c>
-      <c r="BV20" s="47"/>
-      <c r="BW20" s="47"/>
-      <c r="BX20" s="47"/>
-      <c r="BY20" s="54">
+      <c r="BY20" s="32">
         <v>41745</v>
       </c>
-      <c r="BZ20" s="47" t="s">
+      <c r="BZ20" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="CA20" s="47"/>
-      <c r="CB20" s="47" t="s">
+      <c r="CB20" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="CC20" s="47" t="s">
+      <c r="CC20" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="CD20" s="47"/>
-      <c r="CE20" s="47"/>
-      <c r="CF20" s="47"/>
-      <c r="CG20" s="47"/>
-      <c r="CH20" s="47"/>
-      <c r="CI20" s="47"/>
-      <c r="CJ20" s="47"/>
-      <c r="CK20" s="47"/>
-      <c r="CL20" s="47"/>
-      <c r="CM20" s="47"/>
-      <c r="CN20" s="47"/>
-      <c r="CO20" s="47"/>
-      <c r="CP20" s="47"/>
-      <c r="CQ20" s="47"/>
-      <c r="CR20" s="47"/>
-      <c r="CS20" s="47"/>
-      <c r="CT20" s="47"/>
-      <c r="CU20" s="47"/>
-      <c r="CV20" s="47"/>
-      <c r="CW20" s="47"/>
-      <c r="CX20" s="47"/>
-      <c r="CY20" s="47"/>
-      <c r="CZ20" s="47"/>
-      <c r="DA20" s="47"/>
-      <c r="DB20" s="47"/>
-      <c r="DC20" s="47"/>
-      <c r="DD20" s="47"/>
-      <c r="DE20" s="47"/>
-      <c r="DF20" s="49"/>
-      <c r="DG20" s="49"/>
-      <c r="DH20" s="49"/>
-      <c r="DI20" s="49"/>
-      <c r="DJ20" s="49"/>
-      <c r="DK20" s="49"/>
-      <c r="DL20" s="49"/>
-      <c r="DM20" s="49"/>
-      <c r="DN20" s="49"/>
     </row>
     <row r="21" spans="1:118" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="23" t="s">
@@ -9753,15 +9656,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010069CDAA337C336E43B58DBFBB828C56EE" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="40760ae4ad712b56b2f03a21f312bd98">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="29632331-f63e-4ba9-9084-6a4fe1447f8f" xmlns:ns3="c4ca2fa7-6f26-442d-85c3-22f139d78bf8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e42fd9f3eb9e83952b6c5b52116d191" ns2:_="" ns3:_="">
     <xsd:import namespace="29632331-f63e-4ba9-9084-6a4fe1447f8f"/>
@@ -9996,6 +9890,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -10009,14 +9912,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE1ACADB-AA2E-4425-A1C7-48987E81CDEF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09AD1FE6-95EC-4900-A656-2BEF8F9E9F12}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10035,6 +9930,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE1ACADB-AA2E-4425-A1C7-48987E81CDEF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB2AB1AF-7D22-4AC1-B377-5C87D3B9F734}">
   <ds:schemaRefs>

--- a/ExcelToTemplate/Source.xlsx
+++ b/ExcelToTemplate/Source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cf76eb68cee54fc3/Documents/GitHub/python-training/ExcelToTemplate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{AB94D184-D953-40F7-8488-7B4163CAA677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F4DCA1F-07AA-4546-8AE7-D9CE417002C8}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{AB94D184-D953-40F7-8488-7B4163CAA677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{345C09DF-0EA4-4473-85C8-8CC2BCE0EA9A}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="624" xr2:uid="{051F5F2F-B49F-4F58-BE02-03C05ADD24A6}"/>
   </bookViews>
@@ -3720,7 +3720,7 @@
         <v>74</v>
       </c>
       <c r="M3" s="26" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="N3" s="26" t="s">
         <v>298</v>
@@ -9656,6 +9656,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="29632331-f63e-4ba9-9084-6a4fe1447f8f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SteerCo_x0020_date xmlns="29632331-f63e-4ba9-9084-6a4fe1447f8f" xsi:nil="true"/>
+    <TaxCatchAll xmlns="c4ca2fa7-6f26-442d-85c3-22f139d78bf8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010069CDAA337C336E43B58DBFBB828C56EE" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="40760ae4ad712b56b2f03a21f312bd98">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="29632331-f63e-4ba9-9084-6a4fe1447f8f" xmlns:ns3="c4ca2fa7-6f26-442d-85c3-22f139d78bf8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e42fd9f3eb9e83952b6c5b52116d191" ns2:_="" ns3:_="">
     <xsd:import namespace="29632331-f63e-4ba9-9084-6a4fe1447f8f"/>
@@ -9890,28 +9911,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB2AB1AF-7D22-4AC1-B377-5C87D3B9F734}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="29632331-f63e-4ba9-9084-6a4fe1447f8f"/>
+    <ds:schemaRef ds:uri="c4ca2fa7-6f26-442d-85c3-22f139d78bf8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="29632331-f63e-4ba9-9084-6a4fe1447f8f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SteerCo_x0020_date xmlns="29632331-f63e-4ba9-9084-6a4fe1447f8f" xsi:nil="true"/>
-    <TaxCatchAll xmlns="c4ca2fa7-6f26-442d-85c3-22f139d78bf8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE1ACADB-AA2E-4425-A1C7-48987E81CDEF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09AD1FE6-95EC-4900-A656-2BEF8F9E9F12}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9928,23 +9947,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE1ACADB-AA2E-4425-A1C7-48987E81CDEF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB2AB1AF-7D22-4AC1-B377-5C87D3B9F734}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="29632331-f63e-4ba9-9084-6a4fe1447f8f"/>
-    <ds:schemaRef ds:uri="c4ca2fa7-6f26-442d-85c3-22f139d78bf8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/ExcelToTemplate/Source.xlsx
+++ b/ExcelToTemplate/Source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cf76eb68cee54fc3/Documents/GitHub/python-training/ExcelToTemplate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{AB94D184-D953-40F7-8488-7B4163CAA677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{345C09DF-0EA4-4473-85C8-8CC2BCE0EA9A}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{AB94D184-D953-40F7-8488-7B4163CAA677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88683934-55B8-43EC-A937-B4D66AB4B10E}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="624" xr2:uid="{051F5F2F-B49F-4F58-BE02-03C05ADD24A6}"/>
+    <workbookView xWindow="1110" yWindow="1905" windowWidth="15420" windowHeight="11295" tabRatio="624" xr2:uid="{051F5F2F-B49F-4F58-BE02-03C05ADD24A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Rig Information" sheetId="1" r:id="rId1"/>
@@ -1085,9 +1085,6 @@
     <t>DP Email</t>
   </si>
   <si>
-    <t>Alternate DP or DPA</t>
-  </si>
-  <si>
     <t>Name of Alternate DP</t>
   </si>
   <si>
@@ -1950,6 +1947,9 @@
   </si>
   <si>
     <t>Address 1 Test</t>
+  </si>
+  <si>
+    <t>Alternate DP or Alternate DPA</t>
   </si>
 </sst>
 </file>
@@ -3079,7 +3079,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I1" s="12" t="s">
         <v>7</v>
@@ -3112,312 +3112,312 @@
         <v>16</v>
       </c>
       <c r="S1" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="T1" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="12" t="s">
+      <c r="U1" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="V1" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="12" t="s">
+      <c r="W1" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="12" t="s">
+      <c r="X1" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="12" t="s">
+      <c r="Y1" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="12" t="s">
+      <c r="Z1" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="12" t="s">
+      <c r="AA1" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="12" t="s">
+      <c r="AB1" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="12" t="s">
+      <c r="AC1" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="12" t="s">
+      <c r="AD1" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="12" t="s">
+      <c r="AE1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="12" t="s">
+      <c r="AF1" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="12" t="s">
+      <c r="AG1" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="12" t="s">
+      <c r="AH1" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="12" t="s">
+      <c r="AI1" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="13" t="s">
+      <c r="AJ1" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="13" t="s">
+      <c r="AK1" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="13" t="s">
+      <c r="AL1" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AL1" s="13" t="s">
+      <c r="AM1" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="AM1" s="13" t="s">
+      <c r="AN1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AN1" s="13" t="s">
+      <c r="AO1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="AO1" s="13" t="s">
-        <v>39</v>
-      </c>
       <c r="AP1" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ1" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="11" t="s">
+      <c r="AR1" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="11" t="s">
+      <c r="AS1" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="11" t="s">
+      <c r="AT1" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="11" t="s">
+      <c r="AU1" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="11" t="s">
+      <c r="AV1" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="11" t="s">
+      <c r="AW1" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="11" t="s">
+      <c r="AX1" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="11" t="s">
+      <c r="AY1" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="11" t="s">
+      <c r="AZ1" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="11" t="s">
+      <c r="BA1" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="11" t="s">
+      <c r="BB1" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="11" t="s">
+      <c r="BC1" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="11" t="s">
+      <c r="BD1" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="11" t="s">
+      <c r="BE1" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="11" t="s">
+      <c r="BF1" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="11" t="s">
+      <c r="BG1" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="11" t="s">
+      <c r="BH1" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="10" t="s">
+      <c r="BI1" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="10" t="s">
+      <c r="BJ1" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="BK1" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="BL1" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="BM1" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="BN1" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="BO1" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="BP1" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="BQ1" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="BR1" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="BS1" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="BT1" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="BU1" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="BV1" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="BW1" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="BX1" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="BY1" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="BZ1" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="CA1" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="CB1" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="CC1" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="CD1" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="CE1" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="CF1" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="CG1" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="CH1" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="CI1" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="CJ1" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="CK1" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="CL1" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="CM1" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="CN1" s="22" t="s">
+        <v>174</v>
+      </c>
+      <c r="CO1" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="CP1" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="CQ1" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="CR1" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="CS1" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="CT1" s="22" t="s">
+        <v>180</v>
+      </c>
+      <c r="CU1" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="CV1" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="CW1" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="CX1" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="CY1" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="CZ1" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="DA1" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="DB1" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="DC1" s="22" t="s">
+        <v>189</v>
+      </c>
+      <c r="DD1" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="DE1" s="22" t="s">
+        <v>192</v>
+      </c>
+      <c r="DF1" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="BK1" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="BL1" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="BM1" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="BN1" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="BO1" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="BP1" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="BQ1" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="BR1" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="BS1" s="18" t="s">
-        <v>281</v>
-      </c>
-      <c r="BT1" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="BU1" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="BV1" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="BW1" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="BX1" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="BY1" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="BZ1" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="CA1" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="CB1" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="CC1" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="CD1" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="CE1" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="CF1" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="CG1" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="CH1" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="CI1" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="CJ1" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="CK1" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="CL1" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="CM1" s="22" t="s">
-        <v>174</v>
-      </c>
-      <c r="CN1" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="CO1" s="22" t="s">
-        <v>176</v>
-      </c>
-      <c r="CP1" s="22" t="s">
-        <v>177</v>
-      </c>
-      <c r="CQ1" s="22" t="s">
-        <v>178</v>
-      </c>
-      <c r="CR1" s="22" t="s">
-        <v>179</v>
-      </c>
-      <c r="CS1" s="22" t="s">
-        <v>180</v>
-      </c>
-      <c r="CT1" s="22" t="s">
-        <v>181</v>
-      </c>
-      <c r="CU1" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="CV1" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="CW1" s="22" t="s">
-        <v>184</v>
-      </c>
-      <c r="CX1" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="CY1" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="CZ1" s="22" t="s">
-        <v>187</v>
-      </c>
-      <c r="DA1" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="DB1" s="22" t="s">
-        <v>189</v>
-      </c>
-      <c r="DC1" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="DD1" s="22" t="s">
-        <v>192</v>
-      </c>
-      <c r="DE1" s="22" t="s">
-        <v>193</v>
-      </c>
-      <c r="DF1" s="9" t="s">
+      <c r="DG1" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="DG1" s="9" t="s">
+      <c r="DH1" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="DH1" s="9" t="s">
+      <c r="DI1" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="DI1" s="9" t="s">
+      <c r="DJ1" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="DK1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="DJ1" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="DK1" s="9" t="s">
+      <c r="DL1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="DL1" s="9" t="s">
+      <c r="DM1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="DM1" s="9" t="s">
+      <c r="DN1" s="9" t="s">
         <v>67</v>
-      </c>
-      <c r="DN1" s="9" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:118" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="24" t="s">
         <v>71</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>72</v>
       </c>
       <c r="C2" s="25">
         <v>9618898</v>
@@ -3426,90 +3426,90 @@
         <v>5061</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F2" s="27">
         <v>3018270</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J2" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K2" s="26"/>
       <c r="L2" s="26"/>
       <c r="M2" s="26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N2" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="O2" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="P2" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q2" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="R2" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="S2" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="T2" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="O2" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="P2" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q2" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="R2" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="S2" s="26" t="s">
+      <c r="U2" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="T2" s="26" t="s">
+      <c r="V2" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="U2" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="V2" s="28" t="s">
-        <v>300</v>
-      </c>
       <c r="W2" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="X2" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y2" s="40" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z2" s="42" t="s">
         <v>293</v>
       </c>
-      <c r="Z2" s="42" t="s">
+      <c r="AA2" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AB2" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AC2" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="AA2" s="42" t="s">
+      <c r="AD2" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="AB2" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="AC2" s="28" t="s">
+      <c r="AE2" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AF2" s="28" t="s">
         <v>295</v>
       </c>
-      <c r="AD2" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="AE2" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="AF2" s="28" t="s">
+      <c r="AG2" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="AG2" s="26" t="s">
-        <v>297</v>
-      </c>
       <c r="AH2" s="43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AI2" s="26"/>
       <c r="AJ2" s="26"/>
@@ -3522,129 +3522,129 @@
       <c r="AQ2" s="26"/>
       <c r="AR2" s="29"/>
       <c r="AS2" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT2" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU2" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV2" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AW2" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AX2" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AY2" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AZ2" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BA2" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BB2" s="26"/>
       <c r="BC2" s="26"/>
       <c r="BD2" s="26"/>
       <c r="BE2" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BF2" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG2" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BH2" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BI2" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BJ2" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="BK2" s="26" t="s">
         <v>304</v>
       </c>
-      <c r="BK2" s="26" t="s">
-        <v>305</v>
-      </c>
       <c r="BL2" s="26" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="BM2" s="26"/>
       <c r="BN2" s="26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="BO2" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="BP2" s="26" t="s">
         <v>254</v>
       </c>
-      <c r="BP2" s="26" t="s">
+      <c r="BQ2" s="26" t="s">
         <v>255</v>
-      </c>
-      <c r="BQ2" s="26" t="s">
-        <v>256</v>
       </c>
       <c r="BR2" s="26"/>
       <c r="BS2" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BT2" s="26"/>
       <c r="BU2" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BV2" s="26"/>
       <c r="BW2" s="26"/>
       <c r="BX2" s="26" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="BY2" s="32">
         <v>41666</v>
       </c>
       <c r="BZ2" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="CA2" s="26">
         <v>30000</v>
       </c>
       <c r="CB2" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CC2" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CD2" s="26"/>
       <c r="CE2" s="26"/>
       <c r="CF2" s="26"/>
       <c r="CG2" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CH2" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CI2" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CJ2" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CK2" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CL2" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CM2" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CN2" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CO2" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CP2" s="26">
         <v>0</v>
@@ -3669,7 +3669,7 @@
         <v>0</v>
       </c>
       <c r="DB2" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="DC2" s="26"/>
       <c r="DD2" s="26"/>
@@ -3686,10 +3686,10 @@
     </row>
     <row r="3" spans="1:118" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C3" s="25">
         <v>9618903</v>
@@ -3698,249 +3698,249 @@
         <v>5314</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F3" s="27">
         <v>3018270</v>
       </c>
       <c r="G3" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H3" s="26" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I3" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J3" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K3" s="26"/>
       <c r="L3" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M3" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="N3" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="O3" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="P3" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q3" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="R3" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="S3" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="N3" s="26" t="s">
+      <c r="T3" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="O3" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="P3" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q3" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="R3" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="S3" s="26" t="s">
+      <c r="U3" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="T3" s="26" t="s">
+      <c r="V3" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="U3" s="28" t="s">
+      <c r="W3" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="X3" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y3" s="40" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z3" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AA3" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AB3" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AC3" s="28" t="s">
+        <v>294</v>
+      </c>
+      <c r="AD3" s="28" t="s">
+        <v>294</v>
+      </c>
+      <c r="AE3" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AF3" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="AG3" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="AH3" s="26" t="s">
         <v>79</v>
-      </c>
-      <c r="V3" s="28" t="s">
-        <v>300</v>
-      </c>
-      <c r="W3" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="X3" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y3" s="40" t="s">
-        <v>293</v>
-      </c>
-      <c r="Z3" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="AA3" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="AB3" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="AC3" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="AD3" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="AE3" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="AF3" s="28" t="s">
-        <v>296</v>
-      </c>
-      <c r="AG3" s="26" t="s">
-        <v>297</v>
-      </c>
-      <c r="AH3" s="26" t="s">
-        <v>80</v>
       </c>
       <c r="AI3" s="26">
         <v>3018270</v>
       </c>
       <c r="AJ3" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AK3" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL3" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="AL3" s="26" t="s">
+      <c r="AM3" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="AM3" s="26" t="s">
+      <c r="AN3" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="AN3" s="28" t="s">
-        <v>84</v>
-      </c>
       <c r="AO3" s="26" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AP3" s="26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AQ3" s="26">
         <v>9</v>
       </c>
       <c r="AR3" s="29"/>
       <c r="AS3" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT3" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU3" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV3" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AW3" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AX3" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AY3" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AZ3" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BA3" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BB3" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BC3" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BD3" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BE3" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BF3" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG3" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BH3" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BI3" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BJ3" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="BK3" s="26" t="s">
         <v>304</v>
       </c>
-      <c r="BK3" s="26" t="s">
-        <v>305</v>
-      </c>
       <c r="BL3" s="26" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="BM3" s="26"/>
       <c r="BN3" s="26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="BO3" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="BP3" s="26" t="s">
         <v>254</v>
       </c>
-      <c r="BP3" s="26" t="s">
+      <c r="BQ3" s="26" t="s">
         <v>255</v>
-      </c>
-      <c r="BQ3" s="26" t="s">
-        <v>256</v>
       </c>
       <c r="BR3" s="26"/>
       <c r="BS3" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BT3" s="26"/>
       <c r="BU3" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BV3" s="26"/>
       <c r="BW3" s="26"/>
       <c r="BX3" s="26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="BY3" s="32">
         <v>40960</v>
       </c>
       <c r="BZ3" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="CA3" s="26">
         <v>30000</v>
       </c>
       <c r="CB3" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CC3" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CD3" s="26"/>
       <c r="CE3" s="26"/>
       <c r="CF3" s="26"/>
       <c r="CG3" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CH3" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CI3" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CJ3" s="26"/>
       <c r="CK3" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CL3" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CM3" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CN3" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CO3" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CP3" s="26">
         <v>0</v>
@@ -3965,13 +3965,13 @@
         <v>0</v>
       </c>
       <c r="DB3" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="DC3" s="26"/>
       <c r="DD3" s="26"/>
       <c r="DE3" s="26"/>
       <c r="DF3" s="26" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="DG3" s="26"/>
       <c r="DH3" s="28"/>
@@ -3986,10 +3986,10 @@
     </row>
     <row r="4" spans="1:118" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C4" s="25">
         <v>9662631</v>
@@ -3998,249 +3998,249 @@
         <v>5361</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F4" s="27">
         <v>3018270</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H4" s="26" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J4" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K4" s="26"/>
       <c r="L4" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="M4" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="M4" s="26" t="s">
+      <c r="N4" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="O4" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="N4" s="26" t="s">
+      <c r="P4" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q4" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="R4" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="S4" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="T4" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="O4" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="P4" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q4" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="R4" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="S4" s="26" t="s">
+      <c r="U4" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="T4" s="26" t="s">
+      <c r="V4" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="U4" s="28" t="s">
+      <c r="W4" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="X4" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y4" s="40" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z4" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AA4" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AB4" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AC4" s="28" t="s">
+        <v>294</v>
+      </c>
+      <c r="AD4" s="28" t="s">
+        <v>294</v>
+      </c>
+      <c r="AE4" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AF4" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="AG4" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="AH4" s="26" t="s">
         <v>79</v>
-      </c>
-      <c r="V4" s="28" t="s">
-        <v>300</v>
-      </c>
-      <c r="W4" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="X4" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y4" s="40" t="s">
-        <v>293</v>
-      </c>
-      <c r="Z4" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="AA4" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="AB4" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="AC4" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="AD4" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="AE4" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="AF4" s="28" t="s">
-        <v>296</v>
-      </c>
-      <c r="AG4" s="26" t="s">
-        <v>297</v>
-      </c>
-      <c r="AH4" s="26" t="s">
-        <v>80</v>
       </c>
       <c r="AI4" s="26">
         <v>3018270</v>
       </c>
       <c r="AJ4" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AK4" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL4" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="AL4" s="26" t="s">
+      <c r="AM4" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="AM4" s="26" t="s">
+      <c r="AN4" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="AN4" s="28" t="s">
-        <v>84</v>
-      </c>
       <c r="AO4" s="26" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AP4" s="26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AQ4" s="26">
         <v>8</v>
       </c>
       <c r="AR4" s="29"/>
       <c r="AS4" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT4" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU4" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV4" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AW4" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AX4" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AY4" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AZ4" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BA4" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BB4" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BC4" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BD4" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BE4" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BF4" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG4" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BH4" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BI4" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BJ4" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="BK4" s="26" t="s">
         <v>304</v>
       </c>
-      <c r="BK4" s="26" t="s">
-        <v>305</v>
-      </c>
       <c r="BL4" s="26" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="BM4" s="26"/>
       <c r="BN4" s="26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="BO4" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="BP4" s="26" t="s">
         <v>254</v>
       </c>
-      <c r="BP4" s="26" t="s">
+      <c r="BQ4" s="26" t="s">
         <v>255</v>
-      </c>
-      <c r="BQ4" s="26" t="s">
-        <v>256</v>
       </c>
       <c r="BR4" s="26"/>
       <c r="BS4" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BT4" s="26"/>
       <c r="BU4" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BV4" s="26"/>
       <c r="BW4" s="26"/>
       <c r="BX4" s="26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="BY4" s="32">
         <v>41981</v>
       </c>
       <c r="BZ4" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="CA4" s="26">
         <v>30000</v>
       </c>
       <c r="CB4" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CC4" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CD4" s="26"/>
       <c r="CE4" s="26"/>
       <c r="CF4" s="26"/>
       <c r="CG4" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CH4" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CI4" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CJ4" s="26"/>
       <c r="CK4" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CL4" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CM4" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CN4" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CO4" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CP4" s="26">
         <v>0</v>
@@ -4265,7 +4265,7 @@
         <v>0</v>
       </c>
       <c r="DB4" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="DC4" s="26"/>
       <c r="DD4" s="26"/>
@@ -4282,10 +4282,10 @@
     </row>
     <row r="5" spans="1:118" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C5" s="25">
         <v>9629641</v>
@@ -4294,116 +4294,116 @@
         <v>5360</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F5" s="27">
         <v>3018270</v>
       </c>
       <c r="G5" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I5" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J5" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K5" s="26"/>
       <c r="L5" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="M5" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="M5" s="26" t="s">
+      <c r="N5" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="O5" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="N5" s="26" t="s">
+      <c r="P5" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q5" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="R5" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="S5" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="T5" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="O5" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="P5" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q5" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="R5" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="S5" s="26" t="s">
+      <c r="U5" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="T5" s="26" t="s">
+      <c r="V5" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="U5" s="28" t="s">
+      <c r="W5" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="X5" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y5" s="40" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z5" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AA5" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AB5" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AC5" s="28" t="s">
+        <v>294</v>
+      </c>
+      <c r="AD5" s="28" t="s">
+        <v>294</v>
+      </c>
+      <c r="AE5" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AF5" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="AG5" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="AH5" s="26" t="s">
         <v>79</v>
-      </c>
-      <c r="V5" s="28" t="s">
-        <v>300</v>
-      </c>
-      <c r="W5" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="X5" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y5" s="40" t="s">
-        <v>293</v>
-      </c>
-      <c r="Z5" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="AA5" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="AB5" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="AC5" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="AD5" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="AE5" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="AF5" s="28" t="s">
-        <v>296</v>
-      </c>
-      <c r="AG5" s="26" t="s">
-        <v>297</v>
-      </c>
-      <c r="AH5" s="26" t="s">
-        <v>80</v>
       </c>
       <c r="AI5" s="26">
         <v>3018270</v>
       </c>
       <c r="AJ5" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AK5" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL5" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="AL5" s="26" t="s">
+      <c r="AM5" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="AM5" s="26" t="s">
+      <c r="AN5" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="AN5" s="28" t="s">
-        <v>84</v>
-      </c>
       <c r="AO5" s="26" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AP5" s="26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AQ5" s="40">
         <v>8</v>
@@ -4412,124 +4412,124 @@
         <v>46002</v>
       </c>
       <c r="AS5" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT5" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU5" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV5" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AW5" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AX5" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AY5" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AZ5" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BA5" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BB5" s="26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="BC5" s="26" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="BD5" s="26" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="BE5" s="27">
         <v>3018270</v>
       </c>
       <c r="BF5" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG5" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="BH5" s="26" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="BI5" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BJ5" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="BK5" s="26" t="s">
         <v>304</v>
       </c>
-      <c r="BK5" s="26" t="s">
-        <v>305</v>
-      </c>
       <c r="BL5" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="BN5" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="BN5" s="26" t="s">
-        <v>234</v>
-      </c>
       <c r="BO5" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="BP5" s="26" t="s">
         <v>254</v>
       </c>
-      <c r="BP5" s="26" t="s">
+      <c r="BQ5" s="26" t="s">
         <v>255</v>
       </c>
-      <c r="BQ5" s="26" t="s">
+      <c r="BS5" s="35" t="s">
+        <v>302</v>
+      </c>
+      <c r="BU5" s="26" t="s">
         <v>256</v>
       </c>
-      <c r="BS5" s="35" t="s">
-        <v>303</v>
-      </c>
-      <c r="BU5" s="26" t="s">
-        <v>257</v>
-      </c>
       <c r="BX5" s="26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="BY5" s="32">
         <v>42146</v>
       </c>
       <c r="BZ5" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="CA5" s="26">
         <v>30000</v>
       </c>
       <c r="CB5" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CC5" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CG5" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CI5" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CJ5" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CK5" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CL5" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CM5" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CN5" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CO5" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CP5" s="26">
         <v>0</v>
@@ -4547,40 +4547,40 @@
         <v>0</v>
       </c>
       <c r="DB5" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="DF5" s="26" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="DG5" s="26">
         <v>538005361</v>
       </c>
       <c r="DH5" s="28" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="DI5" s="26">
         <v>51732</v>
       </c>
       <c r="DJ5" s="26"/>
       <c r="DK5" s="26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="DL5" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="DM5" s="26">
         <v>5361</v>
       </c>
       <c r="DN5" s="26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:118" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6" s="25">
         <v>8768531</v>
@@ -4589,90 +4589,90 @@
         <v>3627</v>
       </c>
       <c r="E6" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="F6" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="G6" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="H6" s="26" t="s">
         <v>201</v>
       </c>
-      <c r="G6" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="H6" s="26" t="s">
-        <v>202</v>
-      </c>
       <c r="I6" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J6" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K6" s="26"/>
       <c r="L6" s="26"/>
       <c r="M6" s="26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N6" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="O6" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="P6" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q6" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="R6" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="S6" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="T6" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="O6" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="P6" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q6" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="R6" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="S6" s="26" t="s">
+      <c r="U6" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="T6" s="26" t="s">
+      <c r="V6" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="U6" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="V6" s="28" t="s">
-        <v>300</v>
-      </c>
       <c r="W6" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="X6" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y6" s="40" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z6" s="42" t="s">
         <v>293</v>
       </c>
-      <c r="Z6" s="42" t="s">
+      <c r="AA6" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AB6" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AC6" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="AA6" s="42" t="s">
+      <c r="AD6" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="AB6" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="AC6" s="28" t="s">
+      <c r="AE6" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AF6" s="28" t="s">
         <v>295</v>
       </c>
-      <c r="AD6" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="AE6" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="AF6" s="28" t="s">
+      <c r="AG6" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="AG6" s="26" t="s">
-        <v>297</v>
-      </c>
       <c r="AH6" s="26" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AI6" s="26"/>
       <c r="AJ6" s="26"/>
@@ -4687,127 +4687,127 @@
       </c>
       <c r="AR6" s="29"/>
       <c r="AS6" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT6" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU6" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV6" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AW6" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AX6" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AY6" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AZ6" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BA6" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BB6" s="26"/>
       <c r="BC6" s="26"/>
       <c r="BD6" s="26"/>
       <c r="BE6" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BF6" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG6" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BH6" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BI6" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BJ6" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="BK6" s="26" t="s">
         <v>304</v>
       </c>
-      <c r="BK6" s="26" t="s">
-        <v>305</v>
-      </c>
       <c r="BL6" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="BM6" s="26" t="s">
         <v>235</v>
       </c>
-      <c r="BM6" s="26" t="s">
+      <c r="BN6" s="26" t="s">
         <v>236</v>
       </c>
-      <c r="BN6" s="26" t="s">
-        <v>237</v>
-      </c>
       <c r="BO6" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="BP6" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="BQ6" s="26" t="s">
         <v>258</v>
-      </c>
-      <c r="BP6" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="BQ6" s="26" t="s">
-        <v>259</v>
       </c>
       <c r="BR6" s="26"/>
       <c r="BS6" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BT6" s="26"/>
       <c r="BU6" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BV6" s="26"/>
       <c r="BW6" s="26"/>
       <c r="BX6" s="26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="BY6" s="32">
         <v>39917</v>
       </c>
       <c r="BZ6" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="CA6" s="26"/>
       <c r="CB6" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CC6" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CD6" s="26"/>
       <c r="CE6" s="26"/>
       <c r="CF6" s="26"/>
       <c r="CG6" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CH6" s="26"/>
       <c r="CI6" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CJ6" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CK6" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CL6" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CM6" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CN6" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CO6" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CP6" s="26">
         <v>0</v>
@@ -4832,7 +4832,7 @@
         <v>0</v>
       </c>
       <c r="DB6" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="DC6" s="26"/>
       <c r="DD6" s="26"/>
@@ -4849,10 +4849,10 @@
     </row>
     <row r="7" spans="1:118" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7" s="25">
         <v>8769389</v>
@@ -4861,109 +4861,109 @@
         <v>10666</v>
       </c>
       <c r="E7" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="F7" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="F7" s="27" t="s">
-        <v>201</v>
-      </c>
       <c r="G7" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H7" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I7" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J7" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K7" s="26"/>
       <c r="L7" s="26"/>
       <c r="M7" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="N7" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="O7" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="N7" s="26" t="s">
+      <c r="P7" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q7" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="R7" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="S7" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="T7" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="O7" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="P7" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q7" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="R7" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="S7" s="26" t="s">
+      <c r="U7" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="T7" s="26" t="s">
+      <c r="V7" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="U7" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="V7" s="28" t="s">
-        <v>300</v>
-      </c>
       <c r="W7" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="X7" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y7" s="40" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z7" s="42" t="s">
         <v>293</v>
       </c>
-      <c r="Z7" s="42" t="s">
+      <c r="AA7" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AB7" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AC7" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="AA7" s="42" t="s">
+      <c r="AD7" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="AB7" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="AC7" s="28" t="s">
+      <c r="AE7" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AF7" s="28" t="s">
         <v>295</v>
       </c>
-      <c r="AD7" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="AE7" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="AF7" s="28" t="s">
+      <c r="AG7" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="AG7" s="26" t="s">
-        <v>297</v>
-      </c>
       <c r="AH7" s="26" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AI7" s="26">
         <v>5290164</v>
       </c>
       <c r="AJ7" s="26"/>
       <c r="AK7" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL7" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="AL7" s="26" t="s">
+      <c r="AM7" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="AM7" s="26" t="s">
-        <v>83</v>
-      </c>
       <c r="AN7" s="28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AO7" s="26" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AP7" s="26"/>
       <c r="AQ7" s="26">
@@ -4971,81 +4971,81 @@
       </c>
       <c r="AR7" s="29"/>
       <c r="AS7" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT7" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU7" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV7" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AW7" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AX7" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AY7" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AZ7" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BA7" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BB7" s="26"/>
       <c r="BC7" s="26"/>
       <c r="BD7" s="26"/>
       <c r="BE7" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BF7" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG7" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BH7" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BI7" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BJ7" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="BK7" s="26" t="s">
         <v>304</v>
       </c>
-      <c r="BK7" s="26" t="s">
-        <v>305</v>
-      </c>
       <c r="BL7" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="BM7" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="BM7" s="26" t="s">
+      <c r="BN7" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="BN7" s="26" t="s">
-        <v>240</v>
-      </c>
       <c r="BO7" s="26" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BP7" s="26" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BQ7" s="26">
         <v>50450</v>
       </c>
       <c r="BR7" s="26"/>
       <c r="BS7" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BT7" s="26"/>
       <c r="BU7" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BV7" s="26"/>
       <c r="BW7" s="26"/>
@@ -5054,42 +5054,42 @@
         <v>40282</v>
       </c>
       <c r="BZ7" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="CA7" s="26"/>
       <c r="CB7" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CC7" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CD7" s="26"/>
       <c r="CE7" s="26"/>
       <c r="CF7" s="26"/>
       <c r="CG7" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CH7" s="26"/>
       <c r="CI7" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CJ7" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CK7" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CL7" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CM7" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CN7" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CO7" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CP7" s="26">
         <v>0</v>
@@ -5114,7 +5114,7 @@
         <v>0</v>
       </c>
       <c r="DB7" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="DC7" s="26"/>
       <c r="DD7" s="26"/>
@@ -5131,10 +5131,10 @@
     </row>
     <row r="8" spans="1:118" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="23" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" s="25">
         <v>8768361</v>
@@ -5143,229 +5143,229 @@
         <v>10667</v>
       </c>
       <c r="E8" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="F8" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="F8" s="27" t="s">
-        <v>201</v>
-      </c>
       <c r="G8" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H8" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I8" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J8" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K8" s="26"/>
       <c r="L8" s="26"/>
       <c r="M8" s="26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N8" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="O8" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="P8" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q8" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="R8" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="S8" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="T8" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="O8" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="P8" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q8" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="R8" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="S8" s="26" t="s">
+      <c r="U8" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="T8" s="26" t="s">
+      <c r="V8" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="U8" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="V8" s="28" t="s">
-        <v>300</v>
-      </c>
       <c r="W8" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="X8" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y8" s="40" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z8" s="42" t="s">
         <v>293</v>
       </c>
-      <c r="Z8" s="42" t="s">
+      <c r="AA8" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AB8" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AC8" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="AA8" s="42" t="s">
+      <c r="AD8" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="AB8" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="AC8" s="28" t="s">
+      <c r="AE8" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AF8" s="28" t="s">
         <v>295</v>
       </c>
-      <c r="AD8" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="AE8" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="AF8" s="28" t="s">
+      <c r="AG8" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="AG8" s="26" t="s">
-        <v>297</v>
-      </c>
       <c r="AH8" s="26" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AI8" s="26">
         <v>5290164</v>
       </c>
       <c r="AJ8" s="26"/>
       <c r="AK8" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL8" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="AL8" s="26" t="s">
+      <c r="AM8" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="AM8" s="26" t="s">
-        <v>83</v>
-      </c>
       <c r="AN8" s="28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AO8" s="26" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AP8" s="26"/>
       <c r="AQ8" s="26"/>
       <c r="AR8" s="26"/>
       <c r="AS8" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT8" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU8" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV8" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AW8" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AX8" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AY8" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AZ8" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BA8" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BB8" s="30"/>
       <c r="BC8" s="26"/>
       <c r="BD8" s="30"/>
       <c r="BE8" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BF8" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG8" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BH8" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BI8" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BJ8" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="BK8" s="26" t="s">
         <v>304</v>
-      </c>
-      <c r="BK8" s="26" t="s">
-        <v>305</v>
       </c>
       <c r="BL8" s="26"/>
       <c r="BM8" s="26"/>
       <c r="BN8" s="26"/>
       <c r="BO8" s="26" t="s">
+        <v>260</v>
+      </c>
+      <c r="BP8" s="26" t="s">
         <v>261</v>
-      </c>
-      <c r="BP8" s="26" t="s">
-        <v>262</v>
       </c>
       <c r="BQ8" s="26">
         <v>13000000</v>
       </c>
       <c r="BR8" s="26"/>
       <c r="BS8" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BT8" s="26"/>
       <c r="BU8" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BV8" s="26"/>
       <c r="BW8" s="26"/>
       <c r="BX8" s="26" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="BY8" s="32">
         <v>39815</v>
       </c>
       <c r="BZ8" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="CA8" s="26"/>
       <c r="CB8" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CC8" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CD8" s="26"/>
       <c r="CE8" s="26"/>
       <c r="CF8" s="26"/>
       <c r="CG8" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CH8" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CI8" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CJ8" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CK8" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CL8" s="26"/>
       <c r="CM8" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CN8" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CO8" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CP8" s="26">
         <v>0</v>
@@ -5390,7 +5390,7 @@
         <v>0</v>
       </c>
       <c r="DB8" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="DC8" s="26"/>
       <c r="DD8" s="26"/>
@@ -5407,10 +5407,10 @@
     </row>
     <row r="9" spans="1:118" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9" s="25">
         <v>8768373</v>
@@ -5419,237 +5419,237 @@
         <v>10658</v>
       </c>
       <c r="E9" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="F9" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="F9" s="27" t="s">
-        <v>201</v>
-      </c>
       <c r="G9" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I9" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J9" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K9" s="26"/>
       <c r="L9" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="M9" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="M9" s="26" t="s">
+      <c r="N9" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="O9" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="N9" s="26" t="s">
+      <c r="P9" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q9" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="R9" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="S9" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="T9" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="O9" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="P9" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q9" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="R9" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="S9" s="26" t="s">
+      <c r="U9" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="T9" s="26" t="s">
+      <c r="V9" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="U9" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="V9" s="28" t="s">
-        <v>300</v>
-      </c>
       <c r="W9" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="X9" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y9" s="40" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z9" s="42" t="s">
         <v>293</v>
       </c>
-      <c r="Z9" s="42" t="s">
+      <c r="AA9" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AB9" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AC9" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="AA9" s="42" t="s">
+      <c r="AD9" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="AB9" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="AC9" s="28" t="s">
+      <c r="AE9" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AF9" s="28" t="s">
         <v>295</v>
       </c>
-      <c r="AD9" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="AE9" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="AF9" s="28" t="s">
+      <c r="AG9" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="AG9" s="26" t="s">
-        <v>297</v>
-      </c>
       <c r="AH9" s="26" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AI9" s="26">
         <v>6405434</v>
       </c>
       <c r="AJ9" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AK9" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="AL9" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="AL9" s="26" t="s">
+      <c r="AM9" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="AM9" s="26" t="s">
+      <c r="AN9" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="AN9" s="28" t="s">
-        <v>125</v>
-      </c>
       <c r="AO9" s="26" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AP9" s="26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AQ9" s="26">
         <v>6</v>
       </c>
       <c r="AR9" s="29"/>
       <c r="AS9" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT9" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU9" s="26"/>
       <c r="AV9" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AW9" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AX9" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AY9" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AZ9" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BA9" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BB9" s="26"/>
       <c r="BC9" s="26"/>
       <c r="BD9" s="26"/>
       <c r="BE9" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BF9" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG9" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BH9" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BI9" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BJ9" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="BK9" s="26" t="s">
         <v>304</v>
       </c>
-      <c r="BK9" s="26" t="s">
-        <v>305</v>
-      </c>
       <c r="BL9" s="26" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="BM9" s="26"/>
       <c r="BN9" s="26"/>
       <c r="BO9" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="BP9" s="26" t="s">
         <v>263</v>
-      </c>
-      <c r="BP9" s="26" t="s">
-        <v>264</v>
       </c>
       <c r="BQ9" s="26">
         <v>130001</v>
       </c>
       <c r="BR9" s="26"/>
       <c r="BS9" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BT9" s="26"/>
       <c r="BU9" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BV9" s="26"/>
       <c r="BW9" s="26"/>
       <c r="BX9" s="26" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="BY9" s="32">
         <v>40040</v>
       </c>
       <c r="BZ9" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="CA9" s="26"/>
       <c r="CB9" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CC9" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CD9" s="26"/>
       <c r="CE9" s="26"/>
       <c r="CF9" s="26"/>
       <c r="CG9" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CH9" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CI9" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CJ9" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CK9" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CL9" s="26"/>
       <c r="CM9" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CN9" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CO9" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CP9" s="26">
         <v>0</v>
@@ -5674,43 +5674,43 @@
         <v>0</v>
       </c>
       <c r="DB9" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="DC9" s="26"/>
       <c r="DD9" s="26"/>
       <c r="DE9" s="26"/>
       <c r="DF9" s="26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="DG9" s="26">
         <v>538006218</v>
       </c>
       <c r="DH9" s="28" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="DI9" s="26">
         <v>56163</v>
       </c>
       <c r="DJ9" s="26"/>
       <c r="DK9" s="26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="DL9" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="DM9" s="26">
         <v>6218</v>
       </c>
       <c r="DN9" s="26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:118" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" s="25">
         <v>8753079</v>
@@ -5719,57 +5719,57 @@
         <v>1757</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H10" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I10" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J10" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K10" s="26"/>
       <c r="L10" s="26"/>
       <c r="M10" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="N10" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="O10" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="P10" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q10" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="R10" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="S10" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="N10" s="26" t="s">
+      <c r="T10" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="O10" s="28" t="s">
+      <c r="U10" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="P10" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q10" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="R10" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="S10" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="T10" s="26" t="s">
+      <c r="V10" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="U10" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="V10" s="28" t="s">
-        <v>300</v>
-      </c>
       <c r="W10" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="X10" s="26"/>
       <c r="Y10" s="26"/>
@@ -5781,10 +5781,10 @@
       <c r="AE10" s="37"/>
       <c r="AF10" s="28"/>
       <c r="AG10" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AH10" s="26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AI10" s="26"/>
       <c r="AJ10" s="26"/>
@@ -5797,129 +5797,129 @@
       <c r="AQ10" s="26"/>
       <c r="AR10" s="30"/>
       <c r="AS10" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT10" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU10" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV10" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AW10" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AX10" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AY10" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AZ10" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BA10" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BB10" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BC10" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BD10" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BE10" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BF10" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG10" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BH10" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BI10" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BJ10" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="BK10" s="26" t="s">
         <v>304</v>
       </c>
-      <c r="BK10" s="26" t="s">
-        <v>305</v>
-      </c>
       <c r="BL10" s="26" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="BM10" s="26"/>
       <c r="BN10" s="26"/>
       <c r="BO10" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="BP10" s="26" t="s">
         <v>254</v>
       </c>
-      <c r="BP10" s="26" t="s">
+      <c r="BQ10" s="26" t="s">
         <v>255</v>
-      </c>
-      <c r="BQ10" s="26" t="s">
-        <v>256</v>
       </c>
       <c r="BR10" s="26"/>
       <c r="BS10" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BT10" s="26"/>
       <c r="BU10" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BV10" s="26"/>
       <c r="BW10" s="26"/>
       <c r="BX10" s="26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="BY10" s="32">
         <v>27760</v>
       </c>
       <c r="BZ10" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="CA10" s="26"/>
       <c r="CB10" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CC10" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CD10" s="26"/>
       <c r="CE10" s="26"/>
       <c r="CF10" s="26"/>
       <c r="CG10" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CH10" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CI10" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CJ10" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CK10" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CL10" s="26"/>
       <c r="CM10" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CN10" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CO10" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CP10" s="26">
         <v>0</v>
@@ -5944,7 +5944,7 @@
         <v>0</v>
       </c>
       <c r="DB10" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="DC10" s="26"/>
       <c r="DD10" s="26"/>
@@ -5961,10 +5961,10 @@
     </row>
     <row r="11" spans="1:118" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="23" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C11" s="25">
         <v>8767288</v>
@@ -5973,55 +5973,55 @@
         <v>10663</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F11" s="27"/>
       <c r="G11" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I11" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J11" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K11" s="26"/>
       <c r="L11" s="26"/>
       <c r="M11" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="N11" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="O11" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="P11" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q11" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="R11" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="S11" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="N11" s="26" t="s">
+      <c r="T11" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="O11" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="P11" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q11" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="R11" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="S11" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="T11" s="26" t="s">
+      <c r="U11" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="V11" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="U11" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="V11" s="28" t="s">
-        <v>300</v>
-      </c>
       <c r="W11" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="X11" s="26"/>
       <c r="Y11" s="26"/>
@@ -6033,10 +6033,10 @@
       <c r="AE11" s="28"/>
       <c r="AF11" s="28"/>
       <c r="AG11" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AH11" s="26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AI11" s="26"/>
       <c r="AJ11" s="26"/>
@@ -6049,83 +6049,83 @@
       <c r="AQ11" s="26"/>
       <c r="AR11" s="30"/>
       <c r="AS11" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT11" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU11" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV11" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AW11" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AX11" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AY11" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AZ11" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BA11" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BB11" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BC11" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BD11" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BE11" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BF11" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG11" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BH11" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BI11" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BJ11" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="BK11" s="26" t="s">
         <v>304</v>
-      </c>
-      <c r="BK11" s="26" t="s">
-        <v>305</v>
       </c>
       <c r="BL11" s="26"/>
       <c r="BM11" s="26"/>
       <c r="BN11" s="26" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BO11" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="BP11" s="26" t="s">
         <v>254</v>
       </c>
-      <c r="BP11" s="26" t="s">
-        <v>255</v>
-      </c>
       <c r="BQ11" s="26" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="BR11" s="26"/>
       <c r="BS11" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BT11" s="26"/>
       <c r="BU11" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BV11" s="26"/>
       <c r="BW11" s="26"/>
@@ -6134,44 +6134,44 @@
         <v>37628</v>
       </c>
       <c r="BZ11" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="CA11" s="26"/>
       <c r="CB11" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CC11" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CD11" s="26"/>
       <c r="CE11" s="26"/>
       <c r="CF11" s="26"/>
       <c r="CG11" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CH11" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CI11" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CJ11" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CK11" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CL11" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CM11" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CN11" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CO11" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CP11" s="26">
         <v>0</v>
@@ -6196,7 +6196,7 @@
         <v>0</v>
       </c>
       <c r="DB11" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="DC11" s="26"/>
       <c r="DD11" s="26"/>
@@ -6213,10 +6213,10 @@
     </row>
     <row r="12" spans="1:118" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="23" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C12" s="25">
         <v>9664627</v>
@@ -6225,55 +6225,55 @@
         <v>10630</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F12" s="27"/>
       <c r="G12" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H12" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I12" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J12" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K12" s="26"/>
       <c r="L12" s="26"/>
       <c r="M12" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="N12" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="O12" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="P12" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q12" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="R12" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="S12" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="N12" s="26" t="s">
+      <c r="T12" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="O12" s="28" t="s">
+      <c r="U12" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="P12" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q12" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="R12" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="S12" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="T12" s="26" t="s">
+      <c r="V12" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="U12" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="V12" s="28" t="s">
-        <v>300</v>
-      </c>
       <c r="W12" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="X12" s="26"/>
       <c r="Y12" s="26"/>
@@ -6285,10 +6285,10 @@
       <c r="AE12" s="28"/>
       <c r="AF12" s="28"/>
       <c r="AG12" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AH12" s="26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AI12" s="26"/>
       <c r="AJ12" s="26"/>
@@ -6301,131 +6301,131 @@
       <c r="AQ12" s="26"/>
       <c r="AR12" s="30"/>
       <c r="AS12" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT12" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU12" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV12" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AW12" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AX12" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AY12" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AZ12" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BA12" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BB12" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BC12" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BD12" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BE12" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BF12" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG12" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BH12" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BI12" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BJ12" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="BK12" s="26" t="s">
         <v>304</v>
-      </c>
-      <c r="BK12" s="26" t="s">
-        <v>305</v>
       </c>
       <c r="BL12" s="26"/>
       <c r="BM12" s="26"/>
       <c r="BN12" s="26" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="BO12" s="26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BP12" s="26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BQ12" s="26">
         <v>4033</v>
       </c>
       <c r="BR12" s="26"/>
       <c r="BS12" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BT12" s="26"/>
       <c r="BU12" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BV12" s="26"/>
       <c r="BW12" s="26"/>
       <c r="BX12" s="26" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="BY12" s="32">
         <v>42032</v>
       </c>
       <c r="BZ12" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="CA12" s="26"/>
       <c r="CB12" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CC12" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CD12" s="26"/>
       <c r="CE12" s="26"/>
       <c r="CF12" s="26"/>
       <c r="CG12" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CH12" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CI12" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CJ12" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CK12" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CL12" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CM12" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CN12" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CO12" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="CP12" s="26">
         <v>0</v>
@@ -6450,7 +6450,7 @@
         <v>0</v>
       </c>
       <c r="DB12" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="DC12" s="26"/>
       <c r="DD12" s="26"/>
@@ -6467,10 +6467,10 @@
     </row>
     <row r="13" spans="1:118" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="23" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C13" s="25">
         <v>8771552</v>
@@ -6479,55 +6479,55 @@
         <v>10662</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F13" s="39"/>
       <c r="G13" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H13" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I13" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J13" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K13" s="34"/>
       <c r="L13" s="34"/>
       <c r="M13" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="N13" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="O13" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="P13" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q13" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="R13" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="S13" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="N13" s="26" t="s">
+      <c r="T13" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="O13" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="P13" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q13" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="R13" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="S13" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="T13" s="26" t="s">
+      <c r="U13" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="V13" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="U13" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="V13" s="28" t="s">
-        <v>300</v>
-      </c>
       <c r="W13" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="X13" s="34"/>
       <c r="Y13" s="34"/>
@@ -6539,10 +6539,10 @@
       <c r="AE13" s="34"/>
       <c r="AF13" s="34"/>
       <c r="AG13" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AH13" s="26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AI13" s="34"/>
       <c r="AJ13" s="34"/>
@@ -6555,81 +6555,81 @@
       <c r="AQ13" s="34"/>
       <c r="AR13" s="34"/>
       <c r="AS13" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT13" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU13" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV13" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AW13" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AX13" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AY13" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AZ13" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BA13" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BB13" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BC13" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BD13" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BE13" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BF13" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG13" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BH13" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BI13" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BJ13" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="BK13" s="26" t="s">
         <v>304</v>
       </c>
-      <c r="BK13" s="26" t="s">
-        <v>305</v>
-      </c>
       <c r="BL13" s="26" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="BM13" s="26"/>
       <c r="BN13" s="26"/>
       <c r="BO13" s="26"/>
       <c r="BP13" s="26" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="BQ13" s="26">
         <v>2449</v>
       </c>
       <c r="BR13" s="26"/>
       <c r="BS13" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BT13" s="26"/>
       <c r="BU13" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BV13" s="26"/>
       <c r="BW13" s="26"/>
@@ -6638,14 +6638,14 @@
         <v>41858</v>
       </c>
       <c r="BZ13" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="CA13" s="26"/>
       <c r="CB13" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CC13" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CD13" s="26"/>
       <c r="CE13" s="26"/>
@@ -6687,10 +6687,10 @@
     </row>
     <row r="14" spans="1:118" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="23" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C14" s="25">
         <v>8771540</v>
@@ -6699,55 +6699,55 @@
         <v>10631</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F14" s="39"/>
       <c r="G14" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H14" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I14" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J14" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K14" s="34"/>
       <c r="L14" s="34"/>
       <c r="M14" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="N14" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="O14" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="P14" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q14" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="R14" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="S14" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="N14" s="26" t="s">
+      <c r="T14" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="O14" s="28" t="s">
+      <c r="U14" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="P14" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q14" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="R14" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="S14" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="T14" s="26" t="s">
+      <c r="V14" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="U14" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="V14" s="28" t="s">
-        <v>300</v>
-      </c>
       <c r="W14" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="X14" s="34"/>
       <c r="Y14" s="34"/>
@@ -6759,10 +6759,10 @@
       <c r="AE14" s="34"/>
       <c r="AF14" s="34"/>
       <c r="AG14" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AH14" s="26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AI14" s="34"/>
       <c r="AJ14" s="34"/>
@@ -6775,83 +6775,83 @@
       <c r="AQ14" s="34"/>
       <c r="AR14" s="34"/>
       <c r="AS14" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT14" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU14" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV14" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AW14" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AX14" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AY14" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AZ14" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BA14" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BB14" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BC14" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BD14" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BE14" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BF14" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG14" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BH14" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BI14" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BJ14" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="BK14" s="26" t="s">
         <v>304</v>
-      </c>
-      <c r="BK14" s="26" t="s">
-        <v>305</v>
       </c>
       <c r="BL14" s="26"/>
       <c r="BM14" s="26"/>
       <c r="BN14" s="26" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="BO14" s="26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BP14" s="26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BQ14" s="26">
         <v>4033</v>
       </c>
       <c r="BR14" s="26"/>
       <c r="BS14" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BT14" s="26"/>
       <c r="BU14" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BV14" s="26"/>
       <c r="BW14" s="26"/>
@@ -6860,14 +6860,14 @@
         <v>41757</v>
       </c>
       <c r="BZ14" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="CA14" s="26"/>
       <c r="CB14" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CC14" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CD14" s="26"/>
       <c r="CE14" s="26"/>
@@ -6909,10 +6909,10 @@
     </row>
     <row r="15" spans="1:118" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="23" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C15" s="25">
         <v>9711858</v>
@@ -6921,55 +6921,55 @@
         <v>10632</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F15" s="39"/>
       <c r="G15" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H15" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I15" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J15" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K15" s="34"/>
       <c r="L15" s="34"/>
       <c r="M15" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="N15" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="O15" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="P15" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q15" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="R15" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="S15" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="N15" s="26" t="s">
+      <c r="T15" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="O15" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="P15" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q15" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="R15" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="S15" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="T15" s="26" t="s">
+      <c r="U15" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="V15" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="U15" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="V15" s="28" t="s">
-        <v>300</v>
-      </c>
       <c r="W15" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="X15" s="34"/>
       <c r="Y15" s="34"/>
@@ -6981,10 +6981,10 @@
       <c r="AE15" s="34"/>
       <c r="AF15" s="34"/>
       <c r="AG15" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AH15" s="26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AI15" s="34"/>
       <c r="AJ15" s="34"/>
@@ -6997,83 +6997,83 @@
       <c r="AQ15" s="34"/>
       <c r="AR15" s="34"/>
       <c r="AS15" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT15" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU15" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV15" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AW15" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AX15" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AY15" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AZ15" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BA15" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BB15" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BC15" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BD15" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BE15" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BF15" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG15" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BH15" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BI15" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BJ15" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="BK15" s="26" t="s">
         <v>304</v>
-      </c>
-      <c r="BK15" s="26" t="s">
-        <v>305</v>
       </c>
       <c r="BL15" s="26"/>
       <c r="BM15" s="26"/>
       <c r="BN15" s="26" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="BO15" s="26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BP15" s="26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BQ15" s="26">
         <v>4033</v>
       </c>
       <c r="BR15" s="26"/>
       <c r="BS15" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BT15" s="26"/>
       <c r="BU15" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BV15" s="26"/>
       <c r="BW15" s="26"/>
@@ -7082,14 +7082,14 @@
         <v>42739</v>
       </c>
       <c r="BZ15" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="CA15" s="26"/>
       <c r="CB15" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CC15" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CD15" s="26"/>
       <c r="CE15" s="26"/>
@@ -7131,10 +7131,10 @@
     </row>
     <row r="16" spans="1:118" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="23" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C16" s="25">
         <v>8753469</v>
@@ -7143,57 +7143,57 @@
         <v>1830</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F16" s="27">
         <v>5290164</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H16" s="26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J16" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K16" s="34"/>
       <c r="L16" s="34"/>
       <c r="M16" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="N16" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="O16" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="P16" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q16" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="R16" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="S16" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="N16" s="26" t="s">
+      <c r="T16" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="O16" s="28" t="s">
+      <c r="U16" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="P16" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q16" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="R16" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="S16" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="T16" s="26" t="s">
+      <c r="V16" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="U16" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="V16" s="28" t="s">
-        <v>300</v>
-      </c>
       <c r="W16" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="X16" s="34"/>
       <c r="Y16" s="34"/>
@@ -7205,10 +7205,10 @@
       <c r="AE16" s="34"/>
       <c r="AF16" s="34"/>
       <c r="AG16" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AH16" s="26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AI16" s="34"/>
       <c r="AJ16" s="34"/>
@@ -7221,85 +7221,85 @@
       <c r="AQ16" s="34"/>
       <c r="AR16" s="34"/>
       <c r="AS16" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT16" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU16" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV16" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AW16" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AX16" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AY16" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AZ16" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BA16" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BB16" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BC16" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BD16" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BE16" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BF16" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG16" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BH16" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BI16" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BJ16" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="BK16" s="26" t="s">
         <v>304</v>
       </c>
-      <c r="BK16" s="26" t="s">
-        <v>305</v>
-      </c>
       <c r="BL16" s="26" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="BM16" s="26"/>
       <c r="BN16" s="26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="BO16" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="BP16" s="26" t="s">
         <v>254</v>
       </c>
-      <c r="BP16" s="26" t="s">
+      <c r="BQ16" s="26" t="s">
         <v>255</v>
-      </c>
-      <c r="BQ16" s="26" t="s">
-        <v>256</v>
       </c>
       <c r="BR16" s="26"/>
       <c r="BS16" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BT16" s="26"/>
       <c r="BU16" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BV16" s="26"/>
       <c r="BW16" s="26"/>
@@ -7308,14 +7308,14 @@
         <v>30317</v>
       </c>
       <c r="BZ16" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="CA16" s="26"/>
       <c r="CB16" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CC16" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CD16" s="26"/>
       <c r="CE16" s="26"/>
@@ -7357,10 +7357,10 @@
     </row>
     <row r="17" spans="1:118" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="23" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C17" s="25">
         <v>8768220</v>
@@ -7369,55 +7369,55 @@
         <v>10633</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F17" s="39"/>
       <c r="G17" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H17" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I17" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J17" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K17" s="34"/>
       <c r="L17" s="34"/>
       <c r="M17" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="N17" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="O17" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="P17" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q17" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="R17" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="S17" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="N17" s="26" t="s">
+      <c r="T17" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="O17" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="P17" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q17" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="R17" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="S17" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="T17" s="26" t="s">
+      <c r="U17" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="V17" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="U17" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="V17" s="28" t="s">
-        <v>300</v>
-      </c>
       <c r="W17" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="X17" s="34"/>
       <c r="Y17" s="34"/>
@@ -7429,10 +7429,10 @@
       <c r="AE17" s="34"/>
       <c r="AF17" s="34"/>
       <c r="AG17" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AH17" s="26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AI17" s="34"/>
       <c r="AJ17" s="34"/>
@@ -7445,87 +7445,87 @@
       <c r="AQ17" s="34"/>
       <c r="AR17" s="34"/>
       <c r="AS17" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT17" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU17" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV17" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AW17" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AX17" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AY17" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AZ17" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BA17" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BB17" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BC17" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BD17" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BE17" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BF17" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG17" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BH17" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BI17" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BJ17" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="BK17" s="26" t="s">
         <v>304</v>
       </c>
-      <c r="BK17" s="26" t="s">
-        <v>305</v>
-      </c>
       <c r="BL17" s="26" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="BM17" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="BN17" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="BN17" s="26" t="s">
-        <v>246</v>
-      </c>
       <c r="BO17" s="26" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="BP17" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="BQ17" s="26" t="s">
         <v>267</v>
-      </c>
-      <c r="BQ17" s="26" t="s">
-        <v>268</v>
       </c>
       <c r="BR17" s="26"/>
       <c r="BS17" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BT17" s="26"/>
       <c r="BU17" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BV17" s="26"/>
       <c r="BW17" s="26"/>
@@ -7534,14 +7534,14 @@
         <v>39490</v>
       </c>
       <c r="BZ17" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="CA17" s="26"/>
       <c r="CB17" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CC17" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CD17" s="26"/>
       <c r="CE17" s="26"/>
@@ -7583,10 +7583,10 @@
     </row>
     <row r="18" spans="1:118" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C18" s="25">
         <v>8768232</v>
@@ -7595,55 +7595,55 @@
         <v>10660</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F18" s="39"/>
       <c r="G18" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H18" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I18" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J18" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K18" s="34"/>
       <c r="L18" s="34"/>
       <c r="M18" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="N18" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="O18" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="P18" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q18" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="R18" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="S18" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="N18" s="26" t="s">
+      <c r="T18" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="O18" s="28" t="s">
+      <c r="U18" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="P18" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q18" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="R18" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="S18" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="T18" s="26" t="s">
+      <c r="V18" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="U18" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="V18" s="28" t="s">
-        <v>300</v>
-      </c>
       <c r="W18" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="X18" s="34"/>
       <c r="Y18" s="34"/>
@@ -7655,10 +7655,10 @@
       <c r="AE18" s="34"/>
       <c r="AF18" s="34"/>
       <c r="AG18" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AH18" s="26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AI18" s="34"/>
       <c r="AJ18" s="34"/>
@@ -7671,85 +7671,85 @@
       <c r="AQ18" s="34"/>
       <c r="AR18" s="34"/>
       <c r="AS18" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT18" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU18" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV18" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AW18" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AX18" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AY18" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AZ18" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BA18" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BB18" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BC18" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BD18" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BE18" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BF18" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG18" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BH18" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BI18" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BJ18" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="BK18" s="26" t="s">
         <v>304</v>
-      </c>
-      <c r="BK18" s="26" t="s">
-        <v>305</v>
       </c>
       <c r="BL18" s="26">
         <v>2</v>
       </c>
       <c r="BM18" s="26"/>
       <c r="BN18" s="26" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="BO18" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="BP18" s="26" t="s">
         <v>269</v>
-      </c>
-      <c r="BP18" s="26" t="s">
-        <v>270</v>
       </c>
       <c r="BQ18" s="26">
         <v>2830</v>
       </c>
       <c r="BR18" s="26"/>
       <c r="BS18" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BT18" s="26"/>
       <c r="BU18" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BV18" s="26"/>
       <c r="BW18" s="26"/>
@@ -7758,14 +7758,14 @@
         <v>39667</v>
       </c>
       <c r="BZ18" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="CA18" s="26"/>
       <c r="CB18" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CC18" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CD18" s="26"/>
       <c r="CE18" s="26"/>
@@ -7807,10 +7807,10 @@
     </row>
     <row r="19" spans="1:118" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="23" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C19" s="25">
         <v>8768244</v>
@@ -7819,55 +7819,55 @@
         <v>10659</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F19" s="39"/>
       <c r="G19" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H19" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I19" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J19" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K19" s="34"/>
       <c r="L19" s="34"/>
       <c r="M19" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="N19" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="O19" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="P19" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q19" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="R19" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="S19" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="N19" s="26" t="s">
+      <c r="T19" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="O19" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="P19" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q19" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="R19" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="S19" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="T19" s="26" t="s">
+      <c r="U19" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="V19" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="U19" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="V19" s="28" t="s">
-        <v>300</v>
-      </c>
       <c r="W19" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="X19" s="34"/>
       <c r="Y19" s="34"/>
@@ -7879,10 +7879,10 @@
       <c r="AE19" s="34"/>
       <c r="AF19" s="34"/>
       <c r="AG19" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AH19" s="26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AI19" s="34"/>
       <c r="AJ19" s="34"/>
@@ -7895,85 +7895,85 @@
       <c r="AQ19" s="34"/>
       <c r="AR19" s="34"/>
       <c r="AS19" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT19" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU19" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV19" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AW19" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AX19" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AY19" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AZ19" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BA19" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BB19" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BC19" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BD19" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BE19" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BF19" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG19" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BH19" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BI19" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BJ19" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="BK19" s="26" t="s">
         <v>304</v>
       </c>
-      <c r="BK19" s="26" t="s">
-        <v>305</v>
-      </c>
       <c r="BL19" s="26" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="BM19" s="26"/>
       <c r="BN19" s="26" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="BO19" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="BP19" s="26" t="s">
         <v>271</v>
-      </c>
-      <c r="BP19" s="26" t="s">
-        <v>272</v>
       </c>
       <c r="BQ19" s="26">
         <v>28046</v>
       </c>
       <c r="BR19" s="26"/>
       <c r="BS19" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BT19" s="26"/>
       <c r="BU19" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BV19" s="26"/>
       <c r="BW19" s="26"/>
@@ -7982,14 +7982,14 @@
         <v>39833</v>
       </c>
       <c r="BZ19" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="CA19" s="26"/>
       <c r="CB19" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CC19" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CD19" s="26"/>
       <c r="CE19" s="26"/>
@@ -8031,10 +8031,10 @@
     </row>
     <row r="20" spans="1:118" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="44" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B20" s="45" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C20" s="25">
         <v>9624158</v>
@@ -8043,175 +8043,175 @@
         <v>10623</v>
       </c>
       <c r="E20" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="F20" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="F20" s="27" t="s">
-        <v>201</v>
-      </c>
       <c r="G20" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H20" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I20" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J20" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M20" s="26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N20" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="O20" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="P20" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q20" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="R20" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="S20" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="T20" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="O20" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="P20" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q20" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="R20" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="S20" s="26" t="s">
+      <c r="U20" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="T20" s="26" t="s">
+      <c r="V20" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="U20" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="V20" s="28" t="s">
-        <v>300</v>
-      </c>
       <c r="W20" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="X20" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y20" s="26" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Z20" s="41" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AA20" s="27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AB20" s="27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AC20" s="28" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AD20" s="26"/>
       <c r="AE20" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AF20" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="AG20" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="AG20" s="26" t="s">
-        <v>297</v>
-      </c>
       <c r="AH20" s="26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AS20" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT20" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU20" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV20" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AW20" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AX20" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AY20" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AZ20" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BA20" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BE20" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BF20" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG20" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BH20" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BI20" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BJ20" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="BK20" s="26" t="s">
         <v>304</v>
       </c>
-      <c r="BK20" s="26" t="s">
-        <v>305</v>
-      </c>
       <c r="BL20" s="26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="BN20" s="26" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="BO20" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="BP20" s="26" t="s">
         <v>273</v>
-      </c>
-      <c r="BP20" s="26" t="s">
-        <v>274</v>
       </c>
       <c r="BQ20" s="26">
         <v>77042</v>
       </c>
       <c r="BS20" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BU20" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BY20" s="32">
         <v>41745</v>
       </c>
       <c r="BZ20" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="CB20" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CC20" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:118" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C21" s="25">
         <v>9633563</v>
@@ -8220,88 +8220,88 @@
         <v>10664</v>
       </c>
       <c r="E21" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="F21" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="F21" s="27" t="s">
-        <v>201</v>
-      </c>
       <c r="G21" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H21" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I21" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J21" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K21" s="34"/>
       <c r="L21" s="34"/>
       <c r="M21" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="N21" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="O21" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="N21" s="26" t="s">
+      <c r="P21" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q21" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="R21" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="S21" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="T21" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="O21" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="P21" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q21" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="R21" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="S21" s="26" t="s">
+      <c r="U21" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="T21" s="26" t="s">
+      <c r="V21" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="U21" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="V21" s="28" t="s">
-        <v>300</v>
-      </c>
       <c r="W21" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="X21" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y21" s="40" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Z21" s="41" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AA21" s="27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AB21" s="27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AC21" s="28" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AD21" s="26"/>
       <c r="AE21" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="AF21" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="AG21" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="AH21" s="26" t="s">
         <v>230</v>
-      </c>
-      <c r="AF21" s="28" t="s">
-        <v>296</v>
-      </c>
-      <c r="AG21" s="26" t="s">
-        <v>297</v>
-      </c>
-      <c r="AH21" s="26" t="s">
-        <v>231</v>
       </c>
       <c r="AI21" s="34"/>
       <c r="AJ21" s="34"/>
@@ -8314,79 +8314,79 @@
       <c r="AQ21" s="34"/>
       <c r="AR21" s="34"/>
       <c r="AS21" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT21" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU21" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV21" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AW21" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AX21" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AY21" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AZ21" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BA21" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BB21" s="34"/>
       <c r="BC21" s="34"/>
       <c r="BD21" s="34"/>
       <c r="BE21" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BF21" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG21" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BH21" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BI21" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BJ21" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="BK21" s="26" t="s">
         <v>304</v>
       </c>
-      <c r="BK21" s="26" t="s">
-        <v>305</v>
-      </c>
       <c r="BL21" s="26" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="BM21" s="26"/>
       <c r="BN21" s="26" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="BO21" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="BP21" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="BP21" s="26" t="s">
+      <c r="BQ21" s="26" t="s">
         <v>276</v>
-      </c>
-      <c r="BQ21" s="26" t="s">
-        <v>277</v>
       </c>
       <c r="BR21" s="26"/>
       <c r="BS21" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BT21" s="26"/>
       <c r="BU21" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BV21" s="26"/>
       <c r="BW21" s="26"/>
@@ -8395,14 +8395,14 @@
         <v>41904</v>
       </c>
       <c r="BZ21" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="CA21" s="26"/>
       <c r="CB21" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CC21" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CD21" s="26"/>
       <c r="CE21" s="26"/>
@@ -8444,10 +8444,10 @@
     </row>
     <row r="22" spans="1:118" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="23" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C22" s="25">
         <v>9624146</v>
@@ -8456,88 +8456,88 @@
         <v>10665</v>
       </c>
       <c r="E22" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="F22" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="F22" s="27" t="s">
-        <v>201</v>
-      </c>
       <c r="G22" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H22" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I22" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J22" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K22" s="34"/>
       <c r="L22" s="34"/>
       <c r="M22" s="26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N22" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="O22" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="P22" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q22" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="R22" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="S22" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="T22" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="O22" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="P22" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q22" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="R22" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="S22" s="26" t="s">
+      <c r="U22" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="T22" s="26" t="s">
+      <c r="V22" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="U22" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="V22" s="28" t="s">
-        <v>300</v>
-      </c>
       <c r="W22" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="X22" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y22" s="40" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Z22" s="41" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AA22" s="27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AB22" s="27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AC22" s="28" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AD22" s="26"/>
       <c r="AE22" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="AF22" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="AG22" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="AH22" s="26" t="s">
         <v>230</v>
-      </c>
-      <c r="AF22" s="28" t="s">
-        <v>296</v>
-      </c>
-      <c r="AG22" s="26" t="s">
-        <v>297</v>
-      </c>
-      <c r="AH22" s="26" t="s">
-        <v>231</v>
       </c>
       <c r="AI22" s="34"/>
       <c r="AJ22" s="34"/>
@@ -8550,75 +8550,75 @@
       <c r="AQ22" s="34"/>
       <c r="AR22" s="34"/>
       <c r="AS22" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT22" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU22" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV22" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AW22" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AX22" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AY22" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AZ22" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BA22" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BB22" s="34"/>
       <c r="BC22" s="34"/>
       <c r="BD22" s="34"/>
       <c r="BE22" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BF22" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG22" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BH22" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BI22" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BJ22" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="BK22" s="26" t="s">
         <v>304</v>
       </c>
-      <c r="BK22" s="26" t="s">
-        <v>305</v>
-      </c>
       <c r="BL22" s="26" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="BM22" s="26"/>
       <c r="BN22" s="26"/>
       <c r="BO22" s="26"/>
       <c r="BP22" s="26" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="BQ22" s="26">
         <v>2449</v>
       </c>
       <c r="BR22" s="26"/>
       <c r="BS22" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BT22" s="26"/>
       <c r="BU22" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BV22" s="26"/>
       <c r="BW22" s="26"/>
@@ -8627,14 +8627,14 @@
         <v>41694</v>
       </c>
       <c r="BZ22" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="CA22" s="26"/>
       <c r="CB22" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CC22" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CD22" s="26"/>
       <c r="CE22" s="26"/>
@@ -8676,10 +8676,10 @@
     </row>
     <row r="23" spans="1:118" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="23" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C23" s="25">
         <v>9633575</v>
@@ -8688,88 +8688,88 @@
         <v>10378</v>
       </c>
       <c r="E23" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="F23" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="F23" s="27" t="s">
-        <v>201</v>
-      </c>
       <c r="G23" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H23" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I23" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J23" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K23" s="34"/>
       <c r="L23" s="34"/>
       <c r="M23" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="N23" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="O23" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="N23" s="26" t="s">
+      <c r="P23" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q23" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="R23" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="S23" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="T23" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="O23" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="P23" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q23" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="R23" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="S23" s="26" t="s">
+      <c r="U23" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="T23" s="26" t="s">
+      <c r="V23" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="U23" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="V23" s="28" t="s">
-        <v>300</v>
-      </c>
       <c r="W23" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="X23" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y23" s="40" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Z23" s="41" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AA23" s="27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AB23" s="27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AC23" s="28" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AD23" s="26"/>
       <c r="AE23" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="AF23" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="AG23" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="AH23" s="26" t="s">
         <v>230</v>
-      </c>
-      <c r="AF23" s="28" t="s">
-        <v>296</v>
-      </c>
-      <c r="AG23" s="26" t="s">
-        <v>297</v>
-      </c>
-      <c r="AH23" s="26" t="s">
-        <v>231</v>
       </c>
       <c r="AI23" s="34"/>
       <c r="AJ23" s="34"/>
@@ -8782,77 +8782,77 @@
       <c r="AQ23" s="34"/>
       <c r="AR23" s="34"/>
       <c r="AS23" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT23" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU23" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV23" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AW23" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AX23" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AY23" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AZ23" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BA23" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BB23" s="34"/>
       <c r="BC23" s="34"/>
       <c r="BD23" s="34"/>
       <c r="BE23" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BF23" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG23" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BH23" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BI23" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BJ23" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="BK23" s="26" t="s">
         <v>304</v>
-      </c>
-      <c r="BK23" s="26" t="s">
-        <v>305</v>
       </c>
       <c r="BL23" s="26"/>
       <c r="BM23" s="26"/>
       <c r="BN23" s="26" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="BO23" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="BP23" s="26" t="s">
         <v>278</v>
-      </c>
-      <c r="BP23" s="26" t="s">
-        <v>279</v>
       </c>
       <c r="BQ23" s="26">
         <v>6340</v>
       </c>
       <c r="BR23" s="26"/>
       <c r="BS23" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BT23" s="26"/>
       <c r="BU23" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BV23" s="26"/>
       <c r="BW23" s="26"/>
@@ -8861,14 +8861,14 @@
         <v>42041</v>
       </c>
       <c r="BZ23" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="CA23" s="26"/>
       <c r="CB23" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CC23" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CD23" s="26"/>
       <c r="CE23" s="26"/>
@@ -8910,10 +8910,10 @@
     </row>
     <row r="24" spans="1:118" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C24" s="25">
         <v>8753005</v>
@@ -8922,57 +8922,57 @@
         <v>1747</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F24" s="27">
         <v>5290164</v>
       </c>
       <c r="G24" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H24" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I24" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J24" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K24" s="34"/>
       <c r="L24" s="34"/>
       <c r="M24" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="N24" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="O24" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="P24" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q24" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="R24" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="S24" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="N24" s="26" t="s">
+      <c r="T24" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="O24" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="P24" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q24" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="R24" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="S24" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="T24" s="26" t="s">
+      <c r="U24" s="28" t="s">
+        <v>291</v>
+      </c>
+      <c r="V24" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="U24" s="28" t="s">
-        <v>292</v>
-      </c>
-      <c r="V24" s="28" t="s">
-        <v>300</v>
-      </c>
       <c r="W24" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="X24" s="34"/>
       <c r="Y24" s="34"/>
@@ -8984,10 +8984,10 @@
       <c r="AE24" s="34"/>
       <c r="AF24" s="34"/>
       <c r="AG24" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AH24" s="26" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AI24" s="34"/>
       <c r="AJ24" s="34"/>
@@ -9000,87 +9000,87 @@
       <c r="AQ24" s="34"/>
       <c r="AR24" s="34"/>
       <c r="AS24" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT24" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU24" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV24" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AW24" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AX24" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AY24" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AZ24" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BA24" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BB24" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BC24" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BD24" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BE24" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BF24" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG24" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BH24" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BI24" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BJ24" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="BK24" s="26" t="s">
         <v>304</v>
       </c>
-      <c r="BK24" s="26" t="s">
-        <v>305</v>
-      </c>
       <c r="BL24" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="BM24" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="BM24" s="26" t="s">
+      <c r="BN24" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="BN24" s="26" t="s">
-        <v>240</v>
-      </c>
       <c r="BO24" s="26" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BP24" s="26" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BQ24" s="26">
         <v>50450</v>
       </c>
       <c r="BR24" s="26"/>
       <c r="BS24" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BT24" s="26"/>
       <c r="BU24" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BV24" s="26"/>
       <c r="BW24" s="26"/>
@@ -9089,14 +9089,14 @@
         <v>27973</v>
       </c>
       <c r="BZ24" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="CA24" s="26"/>
       <c r="CB24" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CC24" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CD24" s="26"/>
       <c r="CE24" s="26"/>
@@ -9138,10 +9138,10 @@
     </row>
     <row r="25" spans="1:118" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="23" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C25" s="25">
         <v>9697569</v>
@@ -9150,112 +9150,112 @@
         <v>6218</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G25" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H25" s="26" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I25" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J25" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K25" s="34"/>
       <c r="L25" s="34"/>
       <c r="M25" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="N25" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="O25" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="N25" s="26" t="s">
+      <c r="P25" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q25" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="R25" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="S25" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="T25" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="O25" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="P25" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q25" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="R25" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="S25" s="26" t="s">
+      <c r="U25" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="T25" s="26" t="s">
+      <c r="V25" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="U25" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="V25" s="28" t="s">
-        <v>300</v>
-      </c>
       <c r="W25" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="X25" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y25" s="40" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Z25" s="41" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AA25" s="27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AB25" s="27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AC25" s="28" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AD25" s="26"/>
       <c r="AE25" s="28" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AF25" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="AG25" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="AG25" s="26" t="s">
-        <v>297</v>
-      </c>
       <c r="AH25" s="26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AI25" s="27" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ25" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AK25" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="AL25" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="AL25" s="26" t="s">
+      <c r="AM25" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="AM25" s="26" t="s">
+      <c r="AN25" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="AN25" s="28" t="s">
-        <v>125</v>
-      </c>
       <c r="AO25" s="26" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AP25" s="26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AQ25" s="26">
         <v>7</v>
@@ -9264,116 +9264,116 @@
         <v>46009</v>
       </c>
       <c r="AS25" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT25" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU25" s="26" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AV25" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AW25" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AX25" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AY25" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AZ25" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BA25" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BB25" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BC25" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BD25" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BE25" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BF25" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG25" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BH25" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BI25" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BJ25" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="BK25" s="26" t="s">
         <v>304</v>
-      </c>
-      <c r="BK25" s="26" t="s">
-        <v>305</v>
       </c>
       <c r="BL25" s="26"/>
       <c r="BM25" s="26"/>
       <c r="BN25" s="26" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="BO25" s="26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BP25" s="26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BQ25" s="26">
         <v>4033</v>
       </c>
       <c r="BR25" s="26"/>
       <c r="BS25" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BT25" s="26"/>
       <c r="BU25" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BV25" s="26" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="BW25" s="26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BX25" s="26" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="BY25" s="32">
         <v>42566</v>
       </c>
       <c r="BZ25" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="CA25" s="26">
         <v>48960</v>
       </c>
       <c r="CB25" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CC25" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CD25" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CE25" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CF25" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CG25" s="26">
         <v>1</v>
@@ -9465,7 +9465,7 @@
       <c r="DN25" s="34"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="POJkMOaauex2Blwa5tvol2a/YgL3aT72V2yrk18d6wKVwCrB/HlKMA4RJjqnRh+499bn1Cf8hbr0JwM0dUFP2w==" saltValue="YYlKfKMDK7SWuDEegeeokA==" spinCount="100000" sheet="1" formatCells="0" formatRows="0" insertRows="0" insertHyperlinks="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection formatCells="0" formatRows="0" insertRows="0" insertHyperlinks="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="4">
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="B2:B25 J3:J25 W2:W25 CB2:CF25" xr:uid="{C0B0A538-06B5-4E2C-9B32-13FBEE95BF19}">
@@ -9508,137 +9508,137 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="F1" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="F2" s="16" t="s">
         <v>106</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>111</v>
-      </c>
       <c r="E3" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>106</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>114</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="F4" s="16" t="s">
         <v>115</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="F5" s="17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="20" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>149</v>
-      </c>
       <c r="F6" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="21" customFormat="1" ht="210" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
